--- a/facit/ValueSet-kontakttyp-vs.xlsx
+++ b/facit/ValueSet-kontakttyp-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T15:09:43+00:00</t>
+    <t>2026-10-27T15:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/facit/ValueSet-kontakttyp-vs.xlsx
+++ b/facit/ValueSet-kontakttyp-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T15:12:43+00:00</t>
+    <t>2026-10-27T15:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
